--- a/servers/maze_main_server_dev/conf.d/data/maze_energy_affix_rand_rule_v8【迷宫-能力词条-随机规则】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_energy_affix_rand_rule_v8【迷宫-能力词条-随机规则】.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF820247-B4B1-49F9-A49C-CCF3F22217DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C257B2D-B9B8-43A1-9BE8-E056BB618DA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4208,7 +4208,7 @@
         <v>4</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E128" s="4" t="s">
         <v>26</v>
@@ -4237,7 +4237,7 @@
         <v>5</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E129" s="4" t="s">
         <v>26</v>
@@ -4324,7 +4324,7 @@
         <v>8</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E132" s="4" t="s">
         <v>26</v>
